--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -50365,12 +50365,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -50395,22 +50395,25 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O256" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P256" t="n">
+        <v>10</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>0.008168084075657663</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -50419,12 +50422,12 @@
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO256" t="inlineStr">
@@ -50434,70 +50437,65 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR256" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50529,12 +50527,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -50559,33 +50557,36 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O257" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P257" t="n">
+        <v>10</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X257" t="inlineStr">
@@ -50600,12 +50601,12 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB257" t="inlineStr">
@@ -50615,7 +50616,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -50630,7 +50631,7 @@
       </c>
       <c r="AF257" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG257" t="inlineStr">
@@ -50650,12 +50651,12 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM257" t="inlineStr">
@@ -50673,70 +50674,65 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR257" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT257" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50768,12 +50764,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -50807,13 +50803,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -50822,7 +50818,7 @@
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
@@ -50842,7 +50838,7 @@
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR258" t="inlineStr">
@@ -50852,7 +50848,7 @@
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT258" t="n">
@@ -50860,47 +50856,47 @@
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -50932,12 +50928,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -50971,29 +50967,29 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X259" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y259" t="inlineStr">
@@ -51018,7 +51014,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -51053,17 +51049,17 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -51081,7 +51077,7 @@
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR259" t="inlineStr">
@@ -51091,7 +51087,7 @@
       </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT259" t="n">
@@ -51099,45 +51095,448 @@
       </c>
       <c r="AU259" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N260" t="n">
+        <v>1</v>
+      </c>
+      <c r="O260" t="n">
+        <v>1</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO260" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP260" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ260" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT260" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU260" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV259" t="inlineStr">
+      <c r="AV260" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW259" t="inlineStr">
+      <c r="AW260" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX259" t="inlineStr">
+      <c r="AX260" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY259" t="inlineStr">
+      <c r="AY260" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ259" t="inlineStr">
+      <c r="AZ260" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA259" t="inlineStr">
+      <c r="BA260" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB259" t="inlineStr">
+      <c r="BB260" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC259" t="inlineStr">
+      <c r="BC260" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N261" t="n">
+        <v>1</v>
+      </c>
+      <c r="O261" t="n">
+        <v>1</v>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>Aids</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB261" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC261" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD261" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE261" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF261" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG261" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH261" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI261" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ261" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+        </is>
+      </c>
+      <c r="AM261" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN261" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO261" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP261" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ261" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT261" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU261" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA261" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -51259,7 +51658,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10">
@@ -51269,7 +51668,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -51289,7 +51688,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13">
@@ -51321,7 +51720,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40617</v>
+        <v>40627</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -47570,12 +47570,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -47609,13 +47609,16 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>3275</v>
       </c>
       <c r="O242" t="n">
-        <v>0</v>
+        <v>3275</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>1429</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>0.231790455389744</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -47624,7 +47627,7 @@
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
@@ -47634,75 +47637,70 @@
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT242" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -47734,12 +47732,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -47773,29 +47771,29 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>3275</v>
       </c>
       <c r="O243" t="n">
-        <v>0</v>
+        <v>3275</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X243" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y243" t="inlineStr">
@@ -47805,7 +47803,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -47820,7 +47818,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -47835,7 +47833,7 @@
       </c>
       <c r="AF243" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG243" t="inlineStr">
@@ -47855,17 +47853,17 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>China CDC source category 艾滋病; retained as AIDS, not all-stage HIV.</t>
         </is>
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -47873,75 +47871,70 @@
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ243" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT243" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -47973,12 +47966,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -48012,13 +48005,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R244" t="n">
-        <v>0.03537951651591013</v>
+        <v>0</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -48027,7 +48020,7 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -48047,7 +48040,7 @@
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
@@ -48057,7 +48050,7 @@
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT244" t="n">
@@ -48065,47 +48058,47 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48137,12 +48130,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -48176,29 +48169,29 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O245" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y245" t="inlineStr">
@@ -48223,7 +48216,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -48258,17 +48251,17 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48286,7 +48279,7 @@
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
@@ -48296,7 +48289,7 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -48304,47 +48297,47 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48376,12 +48369,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -48415,13 +48408,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O246" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="R246" t="n">
-        <v>0.1303707733931069</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -48430,7 +48423,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -48445,7 +48438,7 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
@@ -48453,57 +48446,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -48535,12 +48533,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -48574,29 +48572,29 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O247" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y247" t="inlineStr">
@@ -48606,7 +48604,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -48621,7 +48619,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -48636,7 +48634,7 @@
       </c>
       <c r="AF247" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG247" t="inlineStr">
@@ -48656,17 +48654,17 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -48679,7 +48677,7 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
@@ -48687,57 +48685,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -48769,12 +48772,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -48799,7 +48802,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -48808,16 +48811,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O248" t="n">
-        <v>13</v>
-      </c>
-      <c r="P248" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="R248" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.1303707733931069</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -48826,12 +48826,12 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
@@ -48851,7 +48851,7 @@
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT248" t="n">
@@ -48864,42 +48864,42 @@
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -48931,12 +48931,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -48961,7 +48961,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -48970,32 +48970,29 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O249" t="n">
-        <v>13</v>
-      </c>
-      <c r="P249" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -49010,7 +49007,7 @@
       </c>
       <c r="AA249" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB249" t="inlineStr">
@@ -49020,7 +49017,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -49060,7 +49057,7 @@
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
@@ -49088,7 +49085,7 @@
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT249" t="n">
@@ -49101,42 +49098,42 @@
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -49198,7 +49195,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -49207,16 +49204,16 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O250" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P250" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R250" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.01061850929835496</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -49360,7 +49357,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -49369,13 +49366,13 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O251" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P251" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
@@ -49597,7 +49594,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -49606,16 +49603,16 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O252" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P252" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R252" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -49759,7 +49756,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -49768,13 +49765,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O253" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P253" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
@@ -49996,7 +49993,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -50005,16 +50002,16 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O254" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P254" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R254" t="n">
-        <v>0.01225212611348649</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -50158,7 +50155,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -50167,13 +50164,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O255" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P255" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -50395,7 +50392,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -50404,16 +50401,16 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O256" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P256" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R256" t="n">
-        <v>0.008168084075657663</v>
+        <v>0.01225212611348649</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -50557,7 +50554,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -50566,13 +50563,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O257" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P257" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -50764,12 +50761,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -50794,22 +50791,25 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P258" t="n">
+        <v>10</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>0.008168084075657663</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -50818,12 +50818,12 @@
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO258" t="inlineStr">
@@ -50833,70 +50833,65 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR258" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50928,12 +50923,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -50958,33 +50953,36 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N259" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O259" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P259" t="n">
+        <v>10</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X259" t="inlineStr">
@@ -50999,12 +50997,12 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB259" t="inlineStr">
@@ -51014,7 +51012,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -51029,7 +51027,7 @@
       </c>
       <c r="AF259" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG259" t="inlineStr">
@@ -51049,12 +51047,12 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM259" t="inlineStr">
@@ -51072,70 +51070,65 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR259" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -51167,12 +51160,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -51206,13 +51199,13 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -51221,7 +51214,7 @@
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
@@ -51241,7 +51234,7 @@
       </c>
       <c r="AQ260" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR260" t="inlineStr">
@@ -51251,7 +51244,7 @@
       </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT260" t="n">
@@ -51259,47 +51252,47 @@
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -51331,12 +51324,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -51370,29 +51363,29 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X261" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y261" t="inlineStr">
@@ -51417,7 +51410,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -51452,17 +51445,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -51480,7 +51473,7 @@
       </c>
       <c r="AQ261" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR261" t="inlineStr">
@@ -51490,7 +51483,7 @@
       </c>
       <c r="AS261" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT261" t="n">
@@ -51498,45 +51491,448 @@
       </c>
       <c r="AU261" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV261" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA261" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB261" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC261" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N262" t="n">
+        <v>1</v>
+      </c>
+      <c r="O262" t="n">
+        <v>1</v>
+      </c>
+      <c r="R262" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO262" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP262" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ262" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR262" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS262" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT262" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU262" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV261" t="inlineStr">
+      <c r="AV262" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW261" t="inlineStr">
+      <c r="AW262" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX261" t="inlineStr">
+      <c r="AX262" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY261" t="inlineStr">
+      <c r="AY262" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ261" t="inlineStr">
+      <c r="AZ262" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA261" t="inlineStr">
+      <c r="BA262" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB261" t="inlineStr">
+      <c r="BB262" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC261" t="inlineStr">
+      <c r="BC262" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N263" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" t="n">
+        <v>1</v>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>Aids</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN263" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO263" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP263" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ263" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR263" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS263" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT263" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU263" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV263" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA263" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB263" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC263" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -51658,7 +52054,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -51668,7 +52064,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="11">
@@ -51688,7 +52084,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13">
@@ -51720,7 +52116,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40627</v>
+        <v>43902</v>
       </c>
     </row>
     <row r="16">
@@ -51730,7 +52126,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10500</v>
+        <v>11929</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -14561,10 +14561,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
@@ -27685,10 +27685,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -27841,10 +27841,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -34911,10 +34911,10 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O177" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -35067,10 +35067,10 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O178" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U178" t="inlineStr">
         <is>
@@ -41299,12 +41299,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -41338,25 +41338,19 @@
         </is>
       </c>
       <c r="N210" t="n">
-        <v>4086</v>
+        <v>5</v>
       </c>
       <c r="O210" t="n">
-        <v>4086</v>
-      </c>
-      <c r="Q210" t="n">
-        <v>1526</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0.2891895574725172</v>
+        <v>5</v>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U210" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -41366,7 +41360,7 @@
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
@@ -41376,12 +41370,12 @@
       </c>
       <c r="AQ210" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="AT210" t="n">
@@ -41389,47 +41383,47 @@
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA210" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB210" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC210" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -41461,12 +41455,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -41500,29 +41494,29 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>4086</v>
+        <v>5</v>
       </c>
       <c r="O211" t="n">
-        <v>4086</v>
+        <v>5</v>
       </c>
       <c r="U211" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="V211" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>SRC_CN_CDC</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>Acquired immunodeficiency syndrome (AIDS)</t>
         </is>
       </c>
       <c r="Y211" t="inlineStr">
@@ -41547,7 +41541,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>country:CN:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -41562,7 +41556,7 @@
       </c>
       <c r="AF211" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG211" t="inlineStr">
@@ -41582,17 +41576,17 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
         <is>
-          <t>China CDC source category 艾滋病; retained as AIDS, not all-stage HIV.</t>
+          <t>PHO IDTO current-year monthly preliminary counts based on the first confirmed AIDS diagnosis in a patient and classified by Diagnosis Status Date. AIDS cases are also included in the HIV series, so the two series are not mutually exclusive.</t>
         </is>
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN211" t="b">
@@ -41600,7 +41594,7 @@
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
@@ -41610,12 +41604,12 @@
       </c>
       <c r="AQ211" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="AT211" t="n">
@@ -41623,47 +41617,47 @@
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -41695,12 +41689,12 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -41734,14 +41728,25 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>91</v>
+        <v>4086</v>
       </c>
       <c r="O212" t="n">
-        <v>91</v>
+        <v>4086</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>1526</v>
+      </c>
+      <c r="R212" t="n">
+        <v>0.2891895574725172</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -41751,70 +41756,70 @@
       </c>
       <c r="AO212" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -41846,12 +41851,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -41885,24 +41890,24 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>91</v>
+        <v>4086</v>
       </c>
       <c r="O213" t="n">
-        <v>91</v>
+        <v>4086</v>
       </c>
       <c r="U213" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_AIDS</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="V213" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_AIDS</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X213" t="inlineStr">
@@ -41917,7 +41922,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -41932,7 +41937,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>country:CN-AH:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
@@ -41947,7 +41952,7 @@
       </c>
       <c r="AF213" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG213" t="inlineStr">
@@ -41967,12 +41972,12 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
         <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+          <t>China CDC source category 艾滋病; retained as AIDS, not all-stage HIV.</t>
         </is>
       </c>
       <c r="AM213" t="inlineStr">
@@ -41985,70 +41990,70 @@
       </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ213" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT213" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -42080,12 +42085,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -42119,10 +42124,10 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>438</v>
+        <v>91</v>
       </c>
       <c r="O214" t="n">
-        <v>438</v>
+        <v>91</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
@@ -42194,7 +42199,7 @@
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
@@ -42231,12 +42236,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -42270,10 +42275,10 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>438</v>
+        <v>91</v>
       </c>
       <c r="O215" t="n">
-        <v>438</v>
+        <v>91</v>
       </c>
       <c r="U215" t="inlineStr">
         <is>
@@ -42317,7 +42322,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>country:CN-CQ:national</t>
+          <t>country:CN-AH:national</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -42428,7 +42433,7 @@
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
@@ -42465,12 +42470,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -42504,10 +42509,10 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="O216" t="n">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -42579,7 +42584,7 @@
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
@@ -42616,12 +42621,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -42655,10 +42660,10 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="O217" t="n">
-        <v>369</v>
+        <v>438</v>
       </c>
       <c r="U217" t="inlineStr">
         <is>
@@ -42702,7 +42707,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
@@ -42813,7 +42818,7 @@
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
@@ -42850,12 +42855,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -42889,10 +42894,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="O218" t="n">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -42964,7 +42969,7 @@
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
@@ -43001,12 +43006,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -43040,10 +43045,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="O219" t="n">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
@@ -43087,7 +43092,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -43198,7 +43203,7 @@
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
@@ -43235,12 +43240,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -43274,10 +43279,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="O220" t="n">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -43349,7 +43354,7 @@
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
@@ -43386,12 +43391,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -43425,10 +43430,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="O221" t="n">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -43472,7 +43477,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -43583,7 +43588,7 @@
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
@@ -43620,12 +43625,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -43659,10 +43664,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="O222" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -43734,7 +43739,7 @@
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
@@ -43771,12 +43776,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -43810,10 +43815,10 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="O223" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="U223" t="inlineStr">
         <is>
@@ -43857,7 +43862,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -43968,7 +43973,7 @@
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
@@ -44005,12 +44010,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -44044,10 +44049,10 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>506</v>
+        <v>67</v>
       </c>
       <c r="O224" t="n">
-        <v>506</v>
+        <v>67</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -44119,7 +44124,7 @@
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
@@ -44156,12 +44161,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -44195,10 +44200,10 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>506</v>
+        <v>67</v>
       </c>
       <c r="O225" t="n">
-        <v>506</v>
+        <v>67</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
@@ -44242,7 +44247,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -44353,7 +44358,7 @@
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
@@ -44390,12 +44395,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -44429,10 +44434,10 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>38</v>
+        <v>506</v>
       </c>
       <c r="O226" t="n">
-        <v>38</v>
+        <v>506</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -44504,7 +44509,7 @@
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
@@ -44541,12 +44546,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -44580,10 +44585,10 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>38</v>
+        <v>506</v>
       </c>
       <c r="O227" t="n">
-        <v>38</v>
+        <v>506</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
@@ -44627,7 +44632,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -44738,7 +44743,7 @@
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
@@ -44775,12 +44780,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -44814,22 +44819,14 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O228" t="n">
-        <v>0</v>
-      </c>
-      <c r="R228" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U228" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -44844,22 +44841,17 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT228" t="n">
@@ -44867,47 +44859,47 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -44939,12 +44931,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -44978,29 +44970,29 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O229" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -45010,7 +45002,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -45025,7 +45017,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -45060,17 +45052,17 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45083,22 +45075,17 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT229" t="n">
@@ -45106,47 +45093,47 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45178,12 +45165,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -45217,13 +45204,13 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -45232,7 +45219,7 @@
       </c>
       <c r="U230" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -45252,7 +45239,7 @@
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR230" t="inlineStr">
@@ -45262,7 +45249,7 @@
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT230" t="n">
@@ -45270,47 +45257,47 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45342,12 +45329,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -45381,29 +45368,29 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -45428,7 +45415,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -45463,17 +45450,17 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -45491,7 +45478,7 @@
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
@@ -45501,7 +45488,7 @@
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT231" t="n">
@@ -45509,47 +45496,47 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45581,12 +45568,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -45620,13 +45607,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="R232" t="n">
-        <v>0.2433587770004662</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -45635,7 +45622,7 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -45650,7 +45637,7 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
@@ -45658,57 +45645,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45740,12 +45732,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -45779,29 +45771,29 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X233" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y233" t="inlineStr">
@@ -45811,7 +45803,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -45826,7 +45818,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -45841,7 +45833,7 @@
       </c>
       <c r="AF233" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG233" t="inlineStr">
@@ -45861,17 +45853,17 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -45884,7 +45876,7 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
@@ -45892,57 +45884,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -45974,12 +45971,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -46004,7 +46001,7 @@
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
@@ -46013,16 +46010,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="O234" t="n">
-        <v>24</v>
-      </c>
-      <c r="P234" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="R234" t="n">
-        <v>0.01960340178157839</v>
+        <v>0.2433587770004662</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -46031,12 +46025,12 @@
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
@@ -46056,7 +46050,7 @@
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT234" t="n">
@@ -46069,42 +46063,42 @@
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -46136,12 +46130,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -46166,7 +46160,7 @@
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
@@ -46175,32 +46169,29 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="O235" t="n">
-        <v>24</v>
-      </c>
-      <c r="P235" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y235" t="inlineStr">
@@ -46215,7 +46206,7 @@
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr">
@@ -46225,7 +46216,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -46265,7 +46256,7 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
@@ -46293,7 +46284,7 @@
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT235" t="n">
@@ -46306,42 +46297,42 @@
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -46403,7 +46394,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -46412,16 +46403,16 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O236" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P236" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="R236" t="n">
-        <v>0.009801700890789196</v>
+        <v>0.01960340178157839</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -46565,7 +46556,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -46574,13 +46565,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O237" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P237" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="U237" t="inlineStr">
         <is>
@@ -46802,7 +46793,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -46964,7 +46955,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -47201,7 +47192,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -47210,16 +47201,16 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O240" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P240" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R240" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -47363,7 +47354,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -47372,13 +47363,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O241" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P241" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
@@ -47570,12 +47561,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -47600,25 +47591,25 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N242" t="n">
-        <v>3275</v>
+        <v>5</v>
       </c>
       <c r="O242" t="n">
-        <v>3275</v>
-      </c>
-      <c r="Q242" t="n">
-        <v>1429</v>
+        <v>5</v>
+      </c>
+      <c r="P242" t="n">
+        <v>5</v>
       </c>
       <c r="R242" t="n">
-        <v>0.231790455389744</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -47627,17 +47618,17 @@
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
@@ -47647,12 +47638,12 @@
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT242" t="n">
@@ -47660,22 +47651,22 @@
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
@@ -47685,22 +47676,22 @@
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47732,12 +47723,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -47762,38 +47753,41 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N243" t="n">
-        <v>3275</v>
+        <v>5</v>
       </c>
       <c r="O243" t="n">
-        <v>3275</v>
+        <v>5</v>
+      </c>
+      <c r="P243" t="n">
+        <v>5</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>SRC_CN_CDC</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X243" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y243" t="inlineStr">
@@ -47808,7 +47802,7 @@
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
@@ -47818,7 +47812,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>country:CN:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -47858,12 +47852,12 @@
       </c>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>China CDC source category 艾滋病; retained as AIDS, not all-stage HIV.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -47871,7 +47865,7 @@
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
@@ -47881,12 +47875,12 @@
       </c>
       <c r="AQ243" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT243" t="n">
@@ -47894,22 +47888,22 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
@@ -47919,22 +47913,22 @@
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47966,12 +47960,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -48005,13 +47999,16 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>0</v>
+        <v>3275</v>
       </c>
       <c r="O244" t="n">
-        <v>0</v>
+        <v>3275</v>
+      </c>
+      <c r="Q244" t="n">
+        <v>1429</v>
       </c>
       <c r="R244" t="n">
-        <v>0</v>
+        <v>0.231790455389744</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -48020,7 +48017,7 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -48030,75 +48027,70 @@
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -48130,12 +48122,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -48169,29 +48161,29 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>0</v>
+        <v>3275</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
+        <v>3275</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y245" t="inlineStr">
@@ -48201,7 +48193,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -48216,7 +48208,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -48231,7 +48223,7 @@
       </c>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG245" t="inlineStr">
@@ -48251,17 +48243,17 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>China CDC source category 艾滋病; retained as AIDS, not all-stage HIV.</t>
         </is>
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48269,75 +48261,70 @@
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -48369,12 +48356,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -48408,13 +48395,13 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>0.03537951651591013</v>
+        <v>0</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -48423,7 +48410,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -48443,7 +48430,7 @@
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
@@ -48453,7 +48440,7 @@
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT246" t="n">
@@ -48461,47 +48448,47 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48533,12 +48520,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -48572,29 +48559,29 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y247" t="inlineStr">
@@ -48619,7 +48606,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -48654,17 +48641,17 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -48682,7 +48669,7 @@
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
@@ -48692,7 +48679,7 @@
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -48700,47 +48687,47 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -48772,12 +48759,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -48811,13 +48798,13 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O248" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="R248" t="n">
-        <v>0.1303707733931069</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -48826,7 +48813,7 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -48841,7 +48828,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
@@ -48849,57 +48836,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -48931,12 +48923,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -48970,29 +48962,29 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O249" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -49002,7 +48994,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -49017,7 +49009,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -49032,7 +49024,7 @@
       </c>
       <c r="AF249" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG249" t="inlineStr">
@@ -49052,17 +49044,17 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -49075,7 +49067,7 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
@@ -49083,57 +49075,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -49165,12 +49162,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -49195,7 +49192,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -49204,16 +49201,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O250" t="n">
-        <v>13</v>
-      </c>
-      <c r="P250" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="R250" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.1303707733931069</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -49222,12 +49216,12 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
@@ -49247,7 +49241,7 @@
       </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT250" t="n">
@@ -49260,42 +49254,42 @@
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -49327,12 +49321,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -49357,7 +49351,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -49366,32 +49360,29 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O251" t="n">
-        <v>13</v>
-      </c>
-      <c r="P251" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X251" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y251" t="inlineStr">
@@ -49406,7 +49397,7 @@
       </c>
       <c r="AA251" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB251" t="inlineStr">
@@ -49416,7 +49407,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -49456,7 +49447,7 @@
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
@@ -49484,7 +49475,7 @@
       </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT251" t="n">
@@ -49497,42 +49488,42 @@
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -49594,7 +49585,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -49603,16 +49594,16 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O252" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P252" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R252" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.01061850929835496</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -49756,7 +49747,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -49765,13 +49756,13 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O253" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P253" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
@@ -49993,7 +49984,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -50002,16 +49993,16 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O254" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P254" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R254" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -50155,7 +50146,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -50164,13 +50155,13 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O255" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P255" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -50392,7 +50383,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -50401,16 +50392,16 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O256" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P256" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R256" t="n">
-        <v>0.01225212611348649</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -50554,7 +50545,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -50563,13 +50554,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O257" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P257" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -50791,7 +50782,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -50800,16 +50791,16 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O258" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P258" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R258" t="n">
-        <v>0.008168084075657663</v>
+        <v>0.01225212611348649</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -50953,7 +50944,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -50962,13 +50953,13 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O259" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P259" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
@@ -51160,12 +51151,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -51190,22 +51181,25 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O260" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P260" t="n">
+        <v>10</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>0.008168084075657663</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -51214,12 +51208,12 @@
       </c>
       <c r="U260" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
@@ -51229,70 +51223,65 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR260" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT260" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -51324,12 +51313,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -51354,33 +51343,36 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O261" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P261" t="n">
+        <v>10</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X261" t="inlineStr">
@@ -51395,12 +51387,12 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB261" t="inlineStr">
@@ -51410,7 +51402,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -51425,7 +51417,7 @@
       </c>
       <c r="AF261" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG261" t="inlineStr">
@@ -51445,12 +51437,12 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM261" t="inlineStr">
@@ -51468,70 +51460,65 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR261" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT261" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -51563,12 +51550,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -51602,13 +51589,13 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R262" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
@@ -51617,7 +51604,7 @@
       </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -51637,7 +51624,7 @@
       </c>
       <c r="AQ262" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR262" t="inlineStr">
@@ -51647,7 +51634,7 @@
       </c>
       <c r="AS262" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT262" t="n">
@@ -51655,47 +51642,47 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -51727,12 +51714,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -51766,29 +51753,29 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W263" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X263" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y263" t="inlineStr">
@@ -51813,7 +51800,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD263" t="inlineStr">
@@ -51848,17 +51835,17 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -51876,7 +51863,7 @@
       </c>
       <c r="AQ263" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR263" t="inlineStr">
@@ -51886,7 +51873,7 @@
       </c>
       <c r="AS263" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT263" t="n">
@@ -51894,45 +51881,448 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV263" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA263" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB263" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC263" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N264" t="n">
+        <v>1</v>
+      </c>
+      <c r="O264" t="n">
+        <v>1</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR264" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT264" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU264" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV263" t="inlineStr">
+      <c r="AV264" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW263" t="inlineStr">
+      <c r="AW264" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX263" t="inlineStr">
+      <c r="AX264" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY263" t="inlineStr">
+      <c r="AY264" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ263" t="inlineStr">
+      <c r="AZ264" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA263" t="inlineStr">
+      <c r="BA264" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB263" t="inlineStr">
+      <c r="BB264" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC263" t="inlineStr">
+      <c r="BC264" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N265" t="n">
+        <v>1</v>
+      </c>
+      <c r="O265" t="n">
+        <v>1</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>Aids</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN265" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT265" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU265" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV265" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA265" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB265" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC265" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -52054,7 +52444,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -52064,7 +52454,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -52084,7 +52474,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -52116,7 +52506,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43902</v>
+        <v>43903</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -52328,6 +52328,405 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N266" t="n">
+        <v>11</v>
+      </c>
+      <c r="O266" t="n">
+        <v>11</v>
+      </c>
+      <c r="P266" t="n">
+        <v>11</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO266" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP266" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ266" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT266" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU266" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV266" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA266" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB266" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC266" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N267" t="n">
+        <v>11</v>
+      </c>
+      <c r="O267" t="n">
+        <v>11</v>
+      </c>
+      <c r="P267" t="n">
+        <v>11</v>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM267" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN267" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT267" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU267" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV267" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA267" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB267" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC267" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -52361,7 +52760,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -52444,7 +52843,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -52454,7 +52853,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -52474,7 +52873,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -52506,7 +52905,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43903</v>
+        <v>43914</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6223,7 +6223,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6625,7 +6625,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13449,7 +13449,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -18690,7 +18690,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -19486,7 +19486,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -19888,7 +19888,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20290,7 +20290,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -20692,7 +20692,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26327,7 +26327,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26729,7 +26729,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27131,7 +27131,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -32749,7 +32749,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -33151,7 +33151,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -33553,7 +33553,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -33955,7 +33955,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -34357,7 +34357,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -34759,7 +34759,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -39590,7 +39590,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -39989,7 +39989,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -40388,7 +40388,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -40787,7 +40787,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -41186,7 +41186,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -41972,7 +41972,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -46251,7 +46251,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -46650,7 +46650,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -47049,7 +47049,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -47448,7 +47448,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -47847,7 +47847,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48243,7 +48243,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -49442,7 +49442,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -49841,7 +49841,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -50240,7 +50240,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -50639,7 +50639,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -51038,7 +51038,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -51437,7 +51437,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -52642,7 +52642,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -52722,6 +52722,405 @@
         </is>
       </c>
       <c r="BC267" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N268" t="n">
+        <v>11</v>
+      </c>
+      <c r="O268" t="n">
+        <v>11</v>
+      </c>
+      <c r="P268" t="n">
+        <v>11</v>
+      </c>
+      <c r="R268" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO268" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP268" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT268" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU268" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV268" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA268" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB268" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC268" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>11</v>
+      </c>
+      <c r="O269" t="n">
+        <v>11</v>
+      </c>
+      <c r="P269" t="n">
+        <v>11</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV269" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB269" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC269" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -52760,7 +53159,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -52843,7 +53242,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
@@ -52853,7 +53252,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11">
@@ -52873,7 +53272,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -52905,7 +53304,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43914</v>
+        <v>43925</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -42855,12 +42855,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -42894,10 +42894,10 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
       <c r="O218" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -42969,7 +42969,7 @@
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
@@ -43006,12 +43006,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -43045,10 +43045,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
       <c r="O219" t="n">
-        <v>369</v>
+        <v>107</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -43203,7 +43203,7 @@
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
@@ -43240,12 +43240,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -43279,10 +43279,10 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="O220" t="n">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
@@ -43391,12 +43391,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -43430,10 +43430,10 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="O221" t="n">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -43588,7 +43588,7 @@
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
@@ -43625,12 +43625,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -43664,10 +43664,10 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="O222" t="n">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -43739,7 +43739,7 @@
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
@@ -43776,12 +43776,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -43815,10 +43815,10 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="O223" t="n">
-        <v>117</v>
+        <v>287</v>
       </c>
       <c r="U223" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -43973,7 +43973,7 @@
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
@@ -44010,12 +44010,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -44049,10 +44049,10 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="O224" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
@@ -44161,12 +44161,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -44200,10 +44200,10 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="O225" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -44358,7 +44358,7 @@
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
@@ -44395,12 +44395,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -44434,10 +44434,10 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>506</v>
+        <v>67</v>
       </c>
       <c r="O226" t="n">
-        <v>506</v>
+        <v>67</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
@@ -44546,12 +44546,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -44585,10 +44585,10 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>506</v>
+        <v>67</v>
       </c>
       <c r="O227" t="n">
-        <v>506</v>
+        <v>67</v>
       </c>
       <c r="U227" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -44743,7 +44743,7 @@
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
@@ -44780,12 +44780,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -44819,10 +44819,10 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>38</v>
+        <v>506</v>
       </c>
       <c r="O228" t="n">
-        <v>38</v>
+        <v>506</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
@@ -44931,12 +44931,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -44970,10 +44970,10 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>38</v>
+        <v>506</v>
       </c>
       <c r="O229" t="n">
-        <v>38</v>
+        <v>506</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -45128,7 +45128,7 @@
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
@@ -45165,12 +45165,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -45204,22 +45204,14 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O230" t="n">
-        <v>0</v>
-      </c>
-      <c r="R230" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U230" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -45234,22 +45226,17 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT230" t="n">
@@ -45257,47 +45244,47 @@
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45329,12 +45316,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -45368,29 +45355,29 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -45400,7 +45387,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -45415,7 +45402,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -45450,17 +45437,17 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -45473,22 +45460,17 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT231" t="n">
@@ -45496,47 +45478,47 @@
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -45568,12 +45550,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -45607,13 +45589,13 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R232" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -45622,7 +45604,7 @@
       </c>
       <c r="U232" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -45642,7 +45624,7 @@
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
@@ -45652,7 +45634,7 @@
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT232" t="n">
@@ -45660,47 +45642,47 @@
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45732,12 +45714,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -45771,29 +45753,29 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X233" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y233" t="inlineStr">
@@ -45818,7 +45800,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -45853,17 +45835,17 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -45881,7 +45863,7 @@
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
@@ -45891,7 +45873,7 @@
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT233" t="n">
@@ -45899,47 +45881,47 @@
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -45971,12 +45953,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -46010,13 +45992,13 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O234" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="R234" t="n">
-        <v>0.2433587770004662</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -46025,7 +46007,7 @@
       </c>
       <c r="U234" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -46040,7 +46022,7 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
@@ -46048,57 +46030,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -46130,12 +46117,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -46169,29 +46156,29 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O235" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y235" t="inlineStr">
@@ -46201,7 +46188,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -46216,7 +46203,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -46231,7 +46218,7 @@
       </c>
       <c r="AF235" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG235" t="inlineStr">
@@ -46251,17 +46238,17 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -46274,7 +46261,7 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
@@ -46282,57 +46269,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -46364,12 +46356,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -46394,7 +46386,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -46403,16 +46395,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="O236" t="n">
-        <v>24</v>
-      </c>
-      <c r="P236" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="R236" t="n">
-        <v>0.01960340178157839</v>
+        <v>0.2433587770004662</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -46421,12 +46410,12 @@
       </c>
       <c r="U236" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
@@ -46446,7 +46435,7 @@
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT236" t="n">
@@ -46459,42 +46448,42 @@
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -46526,12 +46515,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -46556,7 +46545,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -46565,32 +46554,29 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="O237" t="n">
-        <v>24</v>
-      </c>
-      <c r="P237" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="U237" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V237" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X237" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y237" t="inlineStr">
@@ -46605,7 +46591,7 @@
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr">
@@ -46615,7 +46601,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr">
@@ -46655,7 +46641,7 @@
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
@@ -46683,7 +46669,7 @@
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT237" t="n">
@@ -46696,42 +46682,42 @@
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -46793,7 +46779,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -46802,16 +46788,16 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O238" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P238" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="R238" t="n">
-        <v>0.009801700890789196</v>
+        <v>0.01960340178157839</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -46955,7 +46941,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -46964,13 +46950,13 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O239" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P239" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
@@ -47192,7 +47178,7 @@
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
@@ -47354,7 +47340,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -47591,7 +47577,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -47600,16 +47586,16 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O242" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P242" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R242" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -47753,7 +47739,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -47762,13 +47748,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O243" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P243" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
@@ -47960,12 +47946,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -47990,25 +47976,25 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N244" t="n">
-        <v>3275</v>
+        <v>5</v>
       </c>
       <c r="O244" t="n">
-        <v>3275</v>
-      </c>
-      <c r="Q244" t="n">
-        <v>1429</v>
+        <v>5</v>
+      </c>
+      <c r="P244" t="n">
+        <v>5</v>
       </c>
       <c r="R244" t="n">
-        <v>0.231790455389744</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -48017,17 +48003,17 @@
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
@@ -48037,12 +48023,12 @@
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT244" t="n">
@@ -48050,22 +48036,22 @@
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
@@ -48075,22 +48061,22 @@
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48122,12 +48108,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -48152,38 +48138,41 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N245" t="n">
-        <v>3275</v>
+        <v>5</v>
       </c>
       <c r="O245" t="n">
-        <v>3275</v>
+        <v>5</v>
+      </c>
+      <c r="P245" t="n">
+        <v>5</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>SRC_CN_CDC</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y245" t="inlineStr">
@@ -48198,7 +48187,7 @@
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr">
@@ -48208,7 +48197,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>country:CN:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -48248,12 +48237,12 @@
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>China CDC source category 艾滋病; retained as AIDS, not all-stage HIV.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48261,7 +48250,7 @@
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
@@ -48271,12 +48260,12 @@
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -48284,22 +48273,22 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
@@ -48309,22 +48298,22 @@
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48356,12 +48345,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -48395,13 +48384,16 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>0</v>
+        <v>3275</v>
       </c>
       <c r="O246" t="n">
-        <v>0</v>
+        <v>3275</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>1429</v>
       </c>
       <c r="R246" t="n">
-        <v>0</v>
+        <v>0.231790455389744</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -48410,7 +48402,7 @@
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -48420,75 +48412,70 @@
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -48520,12 +48507,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -48559,29 +48546,29 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>3275</v>
       </c>
       <c r="O247" t="n">
-        <v>0</v>
+        <v>3275</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y247" t="inlineStr">
@@ -48591,7 +48578,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -48606,7 +48593,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -48621,7 +48608,7 @@
       </c>
       <c r="AF247" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG247" t="inlineStr">
@@ -48641,17 +48628,17 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>China CDC source category 艾滋病; retained as AIDS, not all-stage HIV.</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -48659,75 +48646,70 @@
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -48759,12 +48741,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -48798,22 +48780,14 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="O248" t="n">
-        <v>2</v>
-      </c>
-      <c r="R248" t="n">
-        <v>0.03537951651591013</v>
+        <v>300</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U248" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -48828,7 +48802,7 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
@@ -48836,14 +48810,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT248" t="n">
@@ -48851,47 +48820,47 @@
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48923,12 +48892,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -48962,29 +48931,29 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="O249" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -48994,7 +48963,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -49009,7 +48978,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -49044,17 +49013,17 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -49067,7 +49036,7 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
@@ -49075,14 +49044,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT249" t="n">
@@ -49090,47 +49054,47 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49162,12 +49126,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -49201,22 +49165,14 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>30</v>
+        <v>289</v>
       </c>
       <c r="O250" t="n">
-        <v>30</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0.1303707733931069</v>
+        <v>289</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -49231,7 +49187,7 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ250" t="inlineStr">
@@ -49241,55 +49197,55 @@
       </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49321,12 +49277,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -49360,29 +49316,29 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>30</v>
+        <v>289</v>
       </c>
       <c r="O251" t="n">
-        <v>30</v>
+        <v>289</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X251" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y251" t="inlineStr">
@@ -49392,7 +49348,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -49407,7 +49363,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -49422,7 +49378,7 @@
       </c>
       <c r="AF251" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG251" t="inlineStr">
@@ -49442,17 +49398,17 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -49465,7 +49421,7 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ251" t="inlineStr">
@@ -49475,55 +49431,55 @@
       </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT251" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49555,12 +49511,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -49585,7 +49541,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -49594,30 +49550,19 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="O252" t="n">
-        <v>13</v>
-      </c>
-      <c r="P252" t="n">
-        <v>13</v>
-      </c>
-      <c r="R252" t="n">
-        <v>0.01061850929835496</v>
+        <v>214</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U252" t="inlineStr">
-        <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
@@ -49627,7 +49572,7 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ252" t="inlineStr">
@@ -49637,55 +49582,55 @@
       </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU252" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49717,12 +49662,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -49747,7 +49692,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -49756,32 +49701,29 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="O253" t="n">
-        <v>13</v>
-      </c>
-      <c r="P253" t="n">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X253" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y253" t="inlineStr">
@@ -49791,12 +49733,12 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB253" t="inlineStr">
@@ -49806,7 +49748,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr">
@@ -49821,7 +49763,7 @@
       </c>
       <c r="AF253" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG253" t="inlineStr">
@@ -49841,17 +49783,17 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -49864,7 +49806,7 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ253" t="inlineStr">
@@ -49874,55 +49816,55 @@
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU253" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49954,12 +49896,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -49984,7 +49926,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -49993,30 +49935,19 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="O254" t="n">
-        <v>9</v>
-      </c>
-      <c r="P254" t="n">
-        <v>9</v>
-      </c>
-      <c r="R254" t="n">
-        <v>0.007351275668091897</v>
+        <v>106</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
@@ -50026,7 +49957,7 @@
       </c>
       <c r="AP254" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ254" t="inlineStr">
@@ -50036,55 +49967,55 @@
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU254" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -50116,12 +50047,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -50146,7 +50077,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -50155,32 +50086,29 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="O255" t="n">
-        <v>9</v>
-      </c>
-      <c r="P255" t="n">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X255" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y255" t="inlineStr">
@@ -50190,12 +50118,12 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr">
@@ -50205,7 +50133,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -50220,7 +50148,7 @@
       </c>
       <c r="AF255" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG255" t="inlineStr">
@@ -50240,17 +50168,17 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -50263,7 +50191,7 @@
       </c>
       <c r="AP255" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ255" t="inlineStr">
@@ -50273,55 +50201,55 @@
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU255" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -50353,12 +50281,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -50383,7 +50311,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -50392,30 +50320,19 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="O256" t="n">
-        <v>14</v>
-      </c>
-      <c r="P256" t="n">
-        <v>14</v>
-      </c>
-      <c r="R256" t="n">
-        <v>0.01143531770592073</v>
+        <v>46</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO256" t="inlineStr">
@@ -50425,7 +50342,7 @@
       </c>
       <c r="AP256" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ256" t="inlineStr">
@@ -50435,55 +50352,55 @@
       </c>
       <c r="AS256" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT256" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -50515,12 +50432,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -50545,7 +50462,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -50554,32 +50471,29 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="O257" t="n">
-        <v>14</v>
-      </c>
-      <c r="P257" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y257" t="inlineStr">
@@ -50589,12 +50503,12 @@
       </c>
       <c r="Z257" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB257" t="inlineStr">
@@ -50604,7 +50518,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -50619,7 +50533,7 @@
       </c>
       <c r="AF257" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG257" t="inlineStr">
@@ -50639,17 +50553,17 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -50662,7 +50576,7 @@
       </c>
       <c r="AP257" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ257" t="inlineStr">
@@ -50672,55 +50586,55 @@
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT257" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -50752,12 +50666,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -50782,7 +50696,7 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -50791,30 +50705,19 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>15</v>
+        <v>395</v>
       </c>
       <c r="O258" t="n">
-        <v>15</v>
-      </c>
-      <c r="P258" t="n">
-        <v>15</v>
-      </c>
-      <c r="R258" t="n">
-        <v>0.01225212611348649</v>
+        <v>395</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U258" t="inlineStr">
-        <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO258" t="inlineStr">
@@ -50824,7 +50727,7 @@
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
@@ -50834,55 +50737,55 @@
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT258" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -50914,12 +50817,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -50944,7 +50847,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
@@ -50953,32 +50856,29 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>15</v>
+        <v>395</v>
       </c>
       <c r="O259" t="n">
-        <v>15</v>
-      </c>
-      <c r="P259" t="n">
-        <v>15</v>
+        <v>395</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X259" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y259" t="inlineStr">
@@ -50988,12 +50888,12 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB259" t="inlineStr">
@@ -51003,7 +50903,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -51018,7 +50918,7 @@
       </c>
       <c r="AF259" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG259" t="inlineStr">
@@ -51038,17 +50938,17 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -51061,7 +50961,7 @@
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
@@ -51071,55 +50971,55 @@
       </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -51151,12 +51051,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -51181,7 +51081,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -51190,30 +51090,19 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="O260" t="n">
-        <v>10</v>
-      </c>
-      <c r="P260" t="n">
-        <v>10</v>
-      </c>
-      <c r="R260" t="n">
-        <v>0.008168084075657663</v>
+        <v>33</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
@@ -51223,7 +51112,7 @@
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
@@ -51233,55 +51122,55 @@
       </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -51313,12 +51202,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -51343,7 +51232,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -51352,32 +51241,29 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="O261" t="n">
-        <v>10</v>
-      </c>
-      <c r="P261" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X261" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y261" t="inlineStr">
@@ -51387,12 +51273,12 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB261" t="inlineStr">
@@ -51402,7 +51288,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -51417,7 +51303,7 @@
       </c>
       <c r="AF261" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG261" t="inlineStr">
@@ -51437,17 +51323,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -51460,7 +51346,7 @@
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
@@ -51470,55 +51356,55 @@
       </c>
       <c r="AS261" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -51580,12 +51466,12 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N262" t="n">
@@ -51744,12 +51630,12 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N263" t="n">
@@ -51983,22 +51869,22 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R264" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -52147,19 +52033,19 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O265" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
@@ -52356,12 +52242,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -52386,25 +52272,22 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N266" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="O266" t="n">
-        <v>11</v>
-      </c>
-      <c r="P266" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="R266" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.1303707733931069</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -52413,12 +52296,12 @@
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO266" t="inlineStr">
@@ -52438,7 +52321,7 @@
       </c>
       <c r="AS266" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT266" t="n">
@@ -52451,42 +52334,42 @@
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -52518,12 +52401,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -52548,41 +52431,38 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N267" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="O267" t="n">
-        <v>11</v>
-      </c>
-      <c r="P267" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X267" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y267" t="inlineStr">
@@ -52597,7 +52477,7 @@
       </c>
       <c r="AA267" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB267" t="inlineStr">
@@ -52607,7 +52487,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD267" t="inlineStr">
@@ -52647,7 +52527,7 @@
       </c>
       <c r="AK267" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM267" t="inlineStr">
@@ -52675,7 +52555,7 @@
       </c>
       <c r="AS267" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT267" t="n">
@@ -52688,42 +52568,42 @@
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -52785,25 +52665,25 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N268" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O268" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P268" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R268" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.01061850929835496</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -52947,22 +52827,22 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N269" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O269" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P269" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
@@ -53121,6 +53001,3206 @@
         </is>
       </c>
       <c r="BC269" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N270" t="n">
+        <v>9</v>
+      </c>
+      <c r="O270" t="n">
+        <v>9</v>
+      </c>
+      <c r="P270" t="n">
+        <v>9</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT270" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV270" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA270" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB270" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC270" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>9</v>
+      </c>
+      <c r="O271" t="n">
+        <v>9</v>
+      </c>
+      <c r="P271" t="n">
+        <v>9</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO271" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP271" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT271" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU271" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV271" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA271" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB271" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC271" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N272" t="n">
+        <v>14</v>
+      </c>
+      <c r="O272" t="n">
+        <v>14</v>
+      </c>
+      <c r="P272" t="n">
+        <v>14</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO272" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP272" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT272" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU272" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV272" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA272" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB272" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC272" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>14</v>
+      </c>
+      <c r="O273" t="n">
+        <v>14</v>
+      </c>
+      <c r="P273" t="n">
+        <v>14</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>15</v>
+      </c>
+      <c r="O274" t="n">
+        <v>15</v>
+      </c>
+      <c r="P274" t="n">
+        <v>15</v>
+      </c>
+      <c r="R274" t="n">
+        <v>0.01225212611348649</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>15</v>
+      </c>
+      <c r="O275" t="n">
+        <v>15</v>
+      </c>
+      <c r="P275" t="n">
+        <v>15</v>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN275" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA275" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB275" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC275" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>10</v>
+      </c>
+      <c r="O276" t="n">
+        <v>10</v>
+      </c>
+      <c r="P276" t="n">
+        <v>10</v>
+      </c>
+      <c r="R276" t="n">
+        <v>0.008168084075657663</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV276" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>10</v>
+      </c>
+      <c r="O277" t="n">
+        <v>10</v>
+      </c>
+      <c r="P277" t="n">
+        <v>10</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA277" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB277" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC277" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AT278" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV278" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA278" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB278" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC278" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN279" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AT279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>1</v>
+      </c>
+      <c r="O280" t="n">
+        <v>1</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>1</v>
+      </c>
+      <c r="O281" t="n">
+        <v>1</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>Aids</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN281" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>11</v>
+      </c>
+      <c r="O282" t="n">
+        <v>11</v>
+      </c>
+      <c r="P282" t="n">
+        <v>11</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>11</v>
+      </c>
+      <c r="O283" t="n">
+        <v>11</v>
+      </c>
+      <c r="P283" t="n">
+        <v>11</v>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN283" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>11</v>
+      </c>
+      <c r="O284" t="n">
+        <v>11</v>
+      </c>
+      <c r="P284" t="n">
+        <v>11</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT284" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>11</v>
+      </c>
+      <c r="O285" t="n">
+        <v>11</v>
+      </c>
+      <c r="P285" t="n">
+        <v>11</v>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB285" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC285" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD285" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE285" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF285" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG285" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH285" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI285" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ285" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK285" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM285" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN285" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT285" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV285" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA285" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB285" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC285" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -53242,7 +56322,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10">
@@ -53252,7 +56332,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>268</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11">
@@ -53272,7 +56352,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -53304,7 +56384,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43925</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -56206,6 +56206,808 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>15</v>
+      </c>
+      <c r="O286" t="n">
+        <v>15</v>
+      </c>
+      <c r="P286" t="n">
+        <v>15</v>
+      </c>
+      <c r="R286" t="n">
+        <v>0.01225212611348649</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT286" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV286" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA286" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB286" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC286" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>15</v>
+      </c>
+      <c r="O287" t="n">
+        <v>15</v>
+      </c>
+      <c r="P287" t="n">
+        <v>15</v>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ287" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK287" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM287" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN287" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT287" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="R288" t="n">
+        <v>0</v>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AT288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV288" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA288" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB288" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC288" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z289" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC289" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD289" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE289" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF289" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG289" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH289" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI289" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ289" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK289" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+        </is>
+      </c>
+      <c r="AM289" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN289" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ289" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AT289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -56239,7 +57041,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -56322,7 +57124,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
@@ -56332,7 +57134,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11">
@@ -56352,7 +57154,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -56384,7 +57186,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>45415</v>
+        <v>45430</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -5436,7 +5436,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -32361,7 +32361,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -39202,7 +39202,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -46248,7 +46248,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -52134,7 +52134,7 @@
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -55072,13 +55072,13 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R280" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -55236,10 +55236,10 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U281" t="inlineStr">
         <is>
@@ -55328,7 +55328,7 @@
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -57186,7 +57186,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>45430</v>
+        <v>45431</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -56633,12 +56633,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -56663,22 +56663,25 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O288" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="P288" t="n">
+        <v>6</v>
       </c>
       <c r="R288" t="n">
-        <v>0</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -56687,12 +56690,12 @@
       </c>
       <c r="U288" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO288" t="inlineStr">
@@ -56702,70 +56705,65 @@
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ288" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR288" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS288" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA288" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB288" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC288" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56797,12 +56795,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -56827,33 +56825,36 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N289" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O289" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="P289" t="n">
+        <v>6</v>
       </c>
       <c r="U289" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X289" t="inlineStr">
@@ -56868,12 +56869,12 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB289" t="inlineStr">
@@ -56883,7 +56884,7 @@
       </c>
       <c r="AC289" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD289" t="inlineStr">
@@ -56898,7 +56899,7 @@
       </c>
       <c r="AF289" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG289" t="inlineStr">
@@ -56918,12 +56919,12 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM289" t="inlineStr">
@@ -56941,68 +56942,466 @@
       </c>
       <c r="AP289" t="inlineStr">
         <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ289" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT289" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ289" t="inlineStr">
+      <c r="AQ290" t="inlineStr">
         <is>
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR289" t="inlineStr">
+      <c r="AR290" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS289" t="inlineStr">
+      <c r="AS290" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
-      <c r="AT289" t="n">
+      <c r="AT290" t="n">
         <v>2</v>
       </c>
-      <c r="AU289" t="inlineStr">
+      <c r="AU290" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV289" t="inlineStr">
+      <c r="AV290" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW289" t="inlineStr">
+      <c r="AW290" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX289" t="inlineStr">
+      <c r="AX290" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY289" t="inlineStr">
+      <c r="AY290" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ289" t="inlineStr">
+      <c r="AZ290" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA289" t="inlineStr">
+      <c r="BA290" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB289" t="inlineStr">
+      <c r="BB290" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC289" t="inlineStr">
+      <c r="BC290" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ291" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK291" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+        </is>
+      </c>
+      <c r="AM291" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN291" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AT291" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -57124,7 +57523,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10">
@@ -57134,7 +57533,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="11">
@@ -57154,7 +57553,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -57186,7 +57585,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>45431</v>
+        <v>45437</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -5436,7 +5436,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN96" t="b">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
@@ -27685,10 +27685,10 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -27841,10 +27841,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O141" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN164" t="b">
@@ -34911,10 +34911,10 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -35067,10 +35067,10 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U178" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN199" t="b">
@@ -46248,7 +46248,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -48345,12 +48345,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -48384,25 +48384,19 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>3275</v>
+        <v>3</v>
       </c>
       <c r="O246" t="n">
-        <v>3275</v>
-      </c>
-      <c r="Q246" t="n">
-        <v>1429</v>
-      </c>
-      <c r="R246" t="n">
-        <v>0.231790455389744</v>
+        <v>3</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
@@ -48412,7 +48406,7 @@
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
@@ -48422,12 +48416,12 @@
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="AT246" t="n">
@@ -48435,47 +48429,47 @@
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48507,12 +48501,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -48546,29 +48540,29 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>3275</v>
+        <v>3</v>
       </c>
       <c r="O247" t="n">
-        <v>3275</v>
+        <v>3</v>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>SRC_CN_CDC</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
         <is>
-          <t>艾滋病</t>
+          <t>Acquired immunodeficiency syndrome (AIDS)</t>
         </is>
       </c>
       <c r="Y247" t="inlineStr">
@@ -48593,7 +48587,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>country:CN:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -48608,7 +48602,7 @@
       </c>
       <c r="AF247" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG247" t="inlineStr">
@@ -48628,17 +48622,17 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>China CDC source category 艾滋病; retained as AIDS, not all-stage HIV.</t>
+          <t>PHO IDTO current-year monthly preliminary counts based on the first confirmed AIDS diagnosis in a patient and classified by Diagnosis Status Date. AIDS cases are also included in the HIV series, so the two series are not mutually exclusive.</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -48646,7 +48640,7 @@
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
@@ -48656,12 +48650,12 @@
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -48669,47 +48663,47 @@
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48741,12 +48735,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -48780,14 +48774,25 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>300</v>
+        <v>3275</v>
       </c>
       <c r="O248" t="n">
-        <v>300</v>
+        <v>3275</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>1429</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0.231790455389744</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -48797,70 +48802,70 @@
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -48892,12 +48897,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -48931,24 +48936,24 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>300</v>
+        <v>3275</v>
       </c>
       <c r="O249" t="n">
-        <v>300</v>
+        <v>3275</v>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_AIDS</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_REPORT_AIDS</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
@@ -48963,7 +48968,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -48978,7 +48983,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>country:CN-CQ:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -48993,7 +48998,7 @@
       </c>
       <c r="AF249" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG249" t="inlineStr">
@@ -49013,12 +49018,12 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+          <t>China CDC source category 艾滋病; retained as AIDS, not all-stage HIV.</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
@@ -49031,70 +49036,70 @@
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT249" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -49126,12 +49131,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -49165,10 +49170,10 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="O250" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -49240,7 +49245,7 @@
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
@@ -49277,12 +49282,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -49316,10 +49321,10 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="O251" t="n">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
@@ -49363,7 +49368,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -49474,7 +49479,7 @@
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
@@ -49511,12 +49516,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -49550,10 +49555,10 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>214</v>
+        <v>289</v>
       </c>
       <c r="O252" t="n">
-        <v>214</v>
+        <v>289</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -49625,7 +49630,7 @@
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
@@ -49662,12 +49667,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -49701,10 +49706,10 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>214</v>
+        <v>289</v>
       </c>
       <c r="O253" t="n">
-        <v>214</v>
+        <v>289</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
@@ -49748,7 +49753,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr">
@@ -49859,7 +49864,7 @@
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
@@ -49896,12 +49901,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -49935,10 +49940,10 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>106</v>
+        <v>214</v>
       </c>
       <c r="O254" t="n">
-        <v>106</v>
+        <v>214</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -50010,7 +50015,7 @@
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
@@ -50047,12 +50052,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -50086,10 +50091,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>106</v>
+        <v>214</v>
       </c>
       <c r="O255" t="n">
-        <v>106</v>
+        <v>214</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -50133,7 +50138,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -50244,7 +50249,7 @@
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
@@ -50281,12 +50286,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -50320,10 +50325,10 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="O256" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -50395,7 +50400,7 @@
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
@@ -50432,12 +50437,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -50471,10 +50476,10 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="O257" t="n">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
@@ -50518,7 +50523,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -50629,7 +50634,7 @@
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
@@ -50666,12 +50671,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -50705,10 +50710,10 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>395</v>
+        <v>46</v>
       </c>
       <c r="O258" t="n">
-        <v>395</v>
+        <v>46</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -50780,7 +50785,7 @@
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
@@ -50817,12 +50822,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -50856,10 +50861,10 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>395</v>
+        <v>46</v>
       </c>
       <c r="O259" t="n">
-        <v>395</v>
+        <v>46</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
@@ -50903,7 +50908,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -51014,7 +51019,7 @@
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
@@ -51051,12 +51056,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -51090,10 +51095,10 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>33</v>
+        <v>395</v>
       </c>
       <c r="O260" t="n">
-        <v>33</v>
+        <v>395</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -51165,7 +51170,7 @@
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
@@ -51202,12 +51207,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -51241,10 +51246,10 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>33</v>
+        <v>395</v>
       </c>
       <c r="O261" t="n">
-        <v>33</v>
+        <v>395</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
@@ -51288,7 +51293,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -51399,7 +51404,7 @@
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
@@ -51436,12 +51441,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -51475,22 +51480,14 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O262" t="n">
-        <v>0</v>
-      </c>
-      <c r="R262" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -51505,22 +51502,17 @@
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ262" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR262" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS262" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT262" t="n">
@@ -51528,47 +51520,47 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -51600,12 +51592,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -51639,29 +51631,29 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="O263" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="W263" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
         </is>
       </c>
       <c r="X263" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y263" t="inlineStr">
@@ -51671,7 +51663,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -51686,7 +51678,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN-SH:national</t>
         </is>
       </c>
       <c r="AD263" t="inlineStr">
@@ -51721,17 +51713,17 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
         </is>
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -51744,22 +51736,17 @@
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ263" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR263" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS263" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_PROV_DC_AIDS; SER_CN_PROV_REPORT_AIDS</t>
         </is>
       </c>
       <c r="AT263" t="n">
@@ -51767,47 +51754,47 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -51839,12 +51826,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -51878,13 +51865,13 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>0.03537951651591013</v>
+        <v>0</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -51893,7 +51880,7 @@
       </c>
       <c r="U264" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA264" t="inlineStr">
@@ -51913,7 +51900,7 @@
       </c>
       <c r="AQ264" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR264" t="inlineStr">
@@ -51923,7 +51910,7 @@
       </c>
       <c r="AS264" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT264" t="n">
@@ -51931,47 +51918,47 @@
       </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -52003,12 +51990,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -52042,29 +52029,29 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W265" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X265" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y265" t="inlineStr">
@@ -52089,7 +52076,7 @@
       </c>
       <c r="AC265" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD265" t="inlineStr">
@@ -52124,17 +52111,17 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN265" t="b">
@@ -52152,7 +52139,7 @@
       </c>
       <c r="AQ265" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR265" t="inlineStr">
@@ -52162,7 +52149,7 @@
       </c>
       <c r="AS265" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT265" t="n">
@@ -52170,47 +52157,47 @@
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -52242,12 +52229,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -52281,13 +52268,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O266" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="R266" t="n">
-        <v>0.1303707733931069</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -52296,7 +52283,7 @@
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -52311,7 +52298,7 @@
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ266" t="inlineStr">
@@ -52319,57 +52306,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS266" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT266" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -52401,12 +52393,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -52440,29 +52432,29 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O267" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X267" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y267" t="inlineStr">
@@ -52472,7 +52464,7 @@
       </c>
       <c r="Z267" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA267" t="inlineStr">
@@ -52487,7 +52479,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD267" t="inlineStr">
@@ -52502,7 +52494,7 @@
       </c>
       <c r="AF267" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG267" t="inlineStr">
@@ -52522,17 +52514,17 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -52545,7 +52537,7 @@
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ267" t="inlineStr">
@@ -52553,57 +52545,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS267" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -52635,12 +52632,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -52665,7 +52662,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -52674,16 +52671,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O268" t="n">
-        <v>13</v>
-      </c>
-      <c r="P268" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="R268" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.1303707733931069</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -52692,12 +52686,12 @@
       </c>
       <c r="U268" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
@@ -52717,7 +52711,7 @@
       </c>
       <c r="AS268" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT268" t="n">
@@ -52730,42 +52724,42 @@
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -52797,12 +52791,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -52827,7 +52821,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -52836,32 +52830,29 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O269" t="n">
-        <v>13</v>
-      </c>
-      <c r="P269" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V269" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W269" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X269" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y269" t="inlineStr">
@@ -52876,7 +52867,7 @@
       </c>
       <c r="AA269" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB269" t="inlineStr">
@@ -52886,7 +52877,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr">
@@ -52926,7 +52917,7 @@
       </c>
       <c r="AK269" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM269" t="inlineStr">
@@ -52954,7 +52945,7 @@
       </c>
       <c r="AS269" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT269" t="n">
@@ -52967,42 +52958,42 @@
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -53064,7 +53055,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -53073,16 +53064,16 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O270" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P270" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R270" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.01061850929835496</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -53226,7 +53217,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -53235,13 +53226,13 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O271" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P271" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
@@ -53463,7 +53454,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -53472,16 +53463,16 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O272" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P272" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="R272" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -53625,7 +53616,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -53634,13 +53625,13 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O273" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="P273" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
@@ -53862,7 +53853,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -53871,16 +53862,16 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O274" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P274" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R274" t="n">
-        <v>0.01225212611348649</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -54024,7 +54015,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -54033,13 +54024,13 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O275" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P275" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
@@ -54261,7 +54252,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -54270,16 +54261,16 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O276" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P276" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R276" t="n">
-        <v>0.008168084075657663</v>
+        <v>0.01225212611348649</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -54423,7 +54414,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -54432,13 +54423,13 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O277" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P277" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
@@ -54630,12 +54621,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -54660,22 +54651,25 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O278" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P278" t="n">
+        <v>10</v>
       </c>
       <c r="R278" t="n">
-        <v>0</v>
+        <v>0.008168084075657663</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -54684,12 +54678,12 @@
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
@@ -54699,70 +54693,65 @@
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ278" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR278" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS278" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54794,12 +54783,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -54824,33 +54813,36 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O279" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="P279" t="n">
+        <v>10</v>
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W279" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X279" t="inlineStr">
@@ -54865,12 +54857,12 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr">
@@ -54880,7 +54872,7 @@
       </c>
       <c r="AC279" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD279" t="inlineStr">
@@ -54895,7 +54887,7 @@
       </c>
       <c r="AF279" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG279" t="inlineStr">
@@ -54915,12 +54907,12 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM279" t="inlineStr">
@@ -54938,70 +54930,65 @@
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ279" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR279" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS279" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55033,12 +55020,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -55072,13 +55059,13 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R280" t="n">
-        <v>0.03537951651591013</v>
+        <v>0</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -55087,7 +55074,7 @@
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -55107,7 +55094,7 @@
       </c>
       <c r="AQ280" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR280" t="inlineStr">
@@ -55117,7 +55104,7 @@
       </c>
       <c r="AS280" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT280" t="n">
@@ -55125,47 +55112,47 @@
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -55197,12 +55184,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -55236,29 +55223,29 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X281" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y281" t="inlineStr">
@@ -55283,7 +55270,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD281" t="inlineStr">
@@ -55318,17 +55305,17 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -55346,7 +55333,7 @@
       </c>
       <c r="AQ281" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR281" t="inlineStr">
@@ -55356,7 +55343,7 @@
       </c>
       <c r="AS281" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT281" t="n">
@@ -55364,47 +55351,47 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -55436,12 +55423,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -55466,7 +55453,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -55475,16 +55462,13 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O282" t="n">
-        <v>11</v>
-      </c>
-      <c r="P282" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R282" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
@@ -55493,12 +55477,12 @@
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO282" t="inlineStr">
@@ -55508,7 +55492,7 @@
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ282" t="inlineStr">
@@ -55516,57 +55500,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS282" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT282" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -55598,12 +55587,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -55628,7 +55617,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -55637,32 +55626,29 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O283" t="n">
-        <v>11</v>
-      </c>
-      <c r="P283" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X283" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y283" t="inlineStr">
@@ -55672,12 +55658,12 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB283" t="inlineStr">
@@ -55687,7 +55673,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD283" t="inlineStr">
@@ -55702,7 +55688,7 @@
       </c>
       <c r="AF283" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG283" t="inlineStr">
@@ -55722,17 +55708,17 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -55745,7 +55731,7 @@
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ283" t="inlineStr">
@@ -55753,57 +55739,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS283" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT283" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -55865,7 +55856,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -56027,7 +56018,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -56264,7 +56255,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -56273,16 +56264,16 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O286" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P286" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="R286" t="n">
-        <v>0.01225212611348649</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
@@ -56426,7 +56417,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -56435,13 +56426,13 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="O287" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="P287" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U287" t="inlineStr">
         <is>
@@ -56663,7 +56654,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -56672,16 +56663,16 @@
         </is>
       </c>
       <c r="N288" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O288" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="P288" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="R288" t="n">
-        <v>0.004900850445394598</v>
+        <v>0.01225212611348649</v>
       </c>
       <c r="S288" t="inlineStr">
         <is>
@@ -56825,7 +56816,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -56834,13 +56825,13 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O289" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="P289" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="U289" t="inlineStr">
         <is>
@@ -57032,12 +57023,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -57062,22 +57053,25 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O290" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="P290" t="n">
+        <v>6</v>
       </c>
       <c r="R290" t="n">
-        <v>0</v>
+        <v>0.004900850445394598</v>
       </c>
       <c r="S290" t="inlineStr">
         <is>
@@ -57086,12 +57080,12 @@
       </c>
       <c r="U290" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO290" t="inlineStr">
@@ -57101,70 +57095,65 @@
       </c>
       <c r="AP290" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ290" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR290" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS290" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT290" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV290" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA290" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB290" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC290" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57196,12 +57185,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -57226,33 +57215,36 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O291" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="P291" t="n">
+        <v>6</v>
       </c>
       <c r="U291" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W291" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X291" t="inlineStr">
@@ -57267,12 +57259,12 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB291" t="inlineStr">
@@ -57282,7 +57274,7 @@
       </c>
       <c r="AC291" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD291" t="inlineStr">
@@ -57297,7 +57289,7 @@
       </c>
       <c r="AF291" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG291" t="inlineStr">
@@ -57317,12 +57309,12 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM291" t="inlineStr">
@@ -57340,70 +57332,871 @@
       </c>
       <c r="AP291" t="inlineStr">
         <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT291" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ291" t="inlineStr">
+      <c r="AQ292" t="inlineStr">
         <is>
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR291" t="inlineStr">
+      <c r="AR292" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS291" t="inlineStr">
+      <c r="AS292" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
-      <c r="AT291" t="n">
+      <c r="AT292" t="n">
         <v>2</v>
       </c>
-      <c r="AU291" t="inlineStr">
+      <c r="AU292" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV291" t="inlineStr">
+      <c r="AV292" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW291" t="inlineStr">
+      <c r="AW292" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX291" t="inlineStr">
+      <c r="AX292" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY291" t="inlineStr">
+      <c r="AY292" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ291" t="inlineStr">
+      <c r="AZ292" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA291" t="inlineStr">
+      <c r="BA292" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB291" t="inlineStr">
+      <c r="BB292" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC291" t="inlineStr">
+      <c r="BC292" t="inlineStr">
         <is>
           <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC293" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD293" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE293" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF293" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG293" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH293" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI293" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ293" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK293" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+        </is>
+      </c>
+      <c r="AM293" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN293" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ293" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AT293" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV293" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA293" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB293" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC293" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ294" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT294" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV294" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY294" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA294" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB294" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC294" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0</v>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>Aids</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB295" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC295" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD295" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE295" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF295" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG295" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH295" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI295" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ295" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK295" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+        </is>
+      </c>
+      <c r="AM295" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN295" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP295" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ295" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR295" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT295" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU295" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV295" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX295" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY295" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA295" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB295" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC295" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -57523,7 +58316,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -57533,7 +58326,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11">
@@ -57553,7 +58346,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">
@@ -57585,7 +58378,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>45437</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -57461,13 +57461,13 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S292" t="inlineStr">
         <is>
@@ -57625,10 +57625,10 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U293" t="inlineStr">
         <is>
@@ -57864,13 +57864,13 @@
         </is>
       </c>
       <c r="N294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R294" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S294" t="inlineStr">
         <is>
@@ -58028,10 +58028,10 @@
         </is>
       </c>
       <c r="N295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U295" t="inlineStr">
         <is>
@@ -58197,6 +58197,405 @@
       <c r="BC295" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>8</v>
+      </c>
+      <c r="O296" t="n">
+        <v>8</v>
+      </c>
+      <c r="P296" t="n">
+        <v>8</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO296" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP296" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ296" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS296" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT296" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU296" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV296" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA296" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB296" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC296" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>8</v>
+      </c>
+      <c r="O297" t="n">
+        <v>8</v>
+      </c>
+      <c r="P297" t="n">
+        <v>8</v>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC297" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD297" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE297" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF297" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG297" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH297" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI297" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ297" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK297" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM297" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN297" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO297" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP297" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ297" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS297" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT297" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU297" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV297" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX297" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY297" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA297" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB297" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC297" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58233,7 +58632,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -58316,7 +58715,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
@@ -58326,7 +58725,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11">
@@ -58346,7 +58745,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -58378,7 +58777,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>45440</v>
+        <v>45450</v>
       </c>
     </row>
     <row r="16">
